--- a/output/pdf_financials_xlsx/MEO.xlsx
+++ b/output/pdf_financials_xlsx/MEO.xlsx
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.047002</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.160163</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.160163</v>
       </c>
     </row>
     <row r="93">
@@ -2327,13 +2327,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.052274</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.131939</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000889</v>
       </c>
     </row>
     <row r="119">
@@ -3083,7 +3083,11 @@
           <t>Reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3448,7 +3452,11 @@
           <t>Reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.047002</v>
       </c>
@@ -3936,7 +3944,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>-0.052274</v>
       </c>

--- a/output/pdf_financials_xlsx/MEO.xlsx
+++ b/output/pdf_financials_xlsx/MEO.xlsx
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.004131</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.098025</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.008135</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.001178</v>
+        <v>0.005309</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.098025</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.008135</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.004131</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.28757</v>
+        <v>0.189545</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.008135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
